--- a/data/data_preparation/celulares/df_relation_matrix.xlsx
+++ b/data/data_preparation/celulares/df_relation_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5EFA10-6A3F-6547-8C63-01F33ED0089D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F335CC4C-B0B0-7D40-B5E9-D56E3C76CA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>customer_need</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Marca</t>
   </si>
   <si>
-    <t>Nombre del sistema operativo</t>
-  </si>
-  <si>
     <t>Tamaño de la pantalla</t>
   </si>
   <si>
@@ -55,12 +52,12 @@
     <t>Tecnología de la pantalla</t>
   </si>
   <si>
+    <t>Tipo de pantalla</t>
+  </si>
+  <si>
     <t>Píxeles por pulgada de la pantalla</t>
   </si>
   <si>
-    <t>Con pantalla táctil</t>
-  </si>
-  <si>
     <t>Capacidad de la batería</t>
   </si>
   <si>
@@ -79,16 +76,19 @@
     <t>Memoria RAM</t>
   </si>
   <si>
-    <t>Con ranura para tarjeta de memoria</t>
-  </si>
-  <si>
     <t>Resolución de la cámara trasera principal</t>
   </si>
   <si>
+    <t>Resolución de video de la cámara trasera</t>
+  </si>
+  <si>
     <t>Resolución de la cámara frontal principal</t>
   </si>
   <si>
-    <t>Cantidad de cámaras traseras</t>
+    <t>Resolución de video de la cámara frontal</t>
+  </si>
+  <si>
+    <t>Modelo del procesador</t>
   </si>
   <si>
     <t>Cantidad de núcleos del procesador</t>
@@ -97,6 +97,21 @@
     <t>Velocidad del procesador</t>
   </si>
   <si>
+    <t>Con flash en la cámara frontal</t>
+  </si>
+  <si>
+    <t>señal</t>
+  </si>
+  <si>
+    <t>sonido</t>
+  </si>
+  <si>
+    <t>sistema</t>
+  </si>
+  <si>
+    <t>diseño</t>
+  </si>
+  <si>
     <t>bateria</t>
   </si>
   <si>
@@ -109,16 +124,10 @@
     <t>pantalla</t>
   </si>
   <si>
-    <t>usar</t>
-  </si>
-  <si>
-    <t>diseño</t>
+    <t>tamaño</t>
   </si>
   <si>
     <t>velocidad</t>
-  </si>
-  <si>
-    <t>marca</t>
   </si>
 </sst>
 </file>
@@ -175,10 +184,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,75 +494,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="96" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -558,7 +585,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -614,10 +641,29 @@
       <c r="U2">
         <v>0</v>
       </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>SUM(B2:Z2)</f>
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -641,16 +687,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -679,10 +725,29 @@
       <c r="U3">
         <v>0</v>
       </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA12" si="0">SUM(B3:Z3)</f>
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -724,415 +789,716 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>3</v>
       </c>
       <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>9</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="S4">
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>9</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
         <v>3</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>9</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>3</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
